--- a/Stats Sheet/Round Gaps/Paradox.xlsx
+++ b/Stats Sheet/Round Gaps/Paradox.xlsx
@@ -346,10 +346,10 @@
     <x:t>Arich</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>Mightyzark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>pkee</x:t>
@@ -3010,15 +3010,9 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D86" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L86" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M86" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="N86" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -3033,9 +3027,15 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D87" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L87" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M87" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N87" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
